--- a/inventory/files/2026-W40/STA_DE_AUTO_2026-W40.xlsx
+++ b/inventory/files/2026-W40/STA_DE_AUTO_2026-W40.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
